--- a/outputs/daily/hr_rankings_2026-08-17.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-17.xlsx
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>77.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>50.9</v>
       </c>
       <c r="R3" t="n">
-        <v>79.3</v>
+        <v>78.3</v>
       </c>
       <c r="S3" t="n">
         <v>86.40000000000001</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>67</v>
+        <v>66.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>50.9</v>
       </c>
       <c r="R8" t="n">
-        <v>79.3</v>
+        <v>78.3</v>
       </c>
       <c r="S8" t="n">
         <v>96.59999999999999</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -4655,27 +4655,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>691023</t>
+          <t>678246</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-17T22:40:00Z</t>
+          <t>2026-08-18T00:05:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4685,22 +4685,22 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Rhett Lowder</t>
+          <t>Shota Imanaga</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>695076</t>
+          <t>684007</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -4718,26 +4718,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>55.9</v>
+        <v>55.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>50.9</v>
+        <v>53</v>
       </c>
       <c r="R16" t="n">
-        <v>79.3</v>
+        <v>46.3</v>
       </c>
       <c r="S16" t="n">
-        <v>94.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>44.1</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -4772,7 +4772,7 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4789,142 +4789,142 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Hot streak: 4 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.6% barrel, 12.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 28.9 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>48.46</t>
+          <t>44.56</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>92.58</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>104.6627</t>
+          <t>100.4699</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4526</t>
+          <t>0.4861</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1956</t>
+          <t>0.2319</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3347</t>
+          <t>0.3638</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>78.87</t>
+          <t>73.05</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>82.77</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>36.22</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>0.2265</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>0.4298</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.1933</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>34.39</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr"/>
@@ -4935,56 +4935,56 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>678246</t>
+          <t>691023</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-18T00:05:00Z</t>
+          <t>2026-08-17T22:40:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Shota Imanaga</t>
+          <t>Rhett Lowder</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>684007</t>
+          <t>695076</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>62.6</v>
+        <v>62.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4998,26 +4998,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>55.1</v>
+        <v>55.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>53</v>
+        <v>50.9</v>
       </c>
       <c r="R17" t="n">
-        <v>46.3</v>
+        <v>78.3</v>
       </c>
       <c r="S17" t="n">
-        <v>96.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>83.59999999999999</v>
+        <v>44.1</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -5052,7 +5052,7 @@
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -5069,142 +5069,142 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Hot streak: 4 HR in last 7 games</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 28.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.6% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher allows elevated contact</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>44.56</t>
+          <t>48.46</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>92.58</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>100.4699</t>
+          <t>104.6627</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4861</t>
+          <t>0.4526</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.2319</t>
+          <t>0.1956</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3638</t>
+          <t>0.3347</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>73.05</t>
+          <t>78.87</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>82.77</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>36.22</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.2265</t>
+          <t>0.175</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.4298</t>
+          <t>0.456</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1933</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr"/>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -7504,7 +7504,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>59.1</v>
+        <v>59</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>27.2</v>
       </c>
       <c r="R26" t="n">
-        <v>79.3</v>
+        <v>78.3</v>
       </c>
       <c r="S26" t="n">
         <v>100</v>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -8855,27 +8855,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>802139</t>
+          <t>695600</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>JJ Wetherholt</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-17T22:40:00Z</t>
+          <t>2026-08-17T23:40:00Z</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Rhett Lowder</t>
+          <t>Mason Barnett</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>695076</t>
+          <t>686930</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -8918,17 +8918,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>37.5</v>
+        <v>53.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>50.9</v>
+        <v>48.6</v>
       </c>
       <c r="R31" t="n">
-        <v>79.3</v>
+        <v>47.7</v>
       </c>
       <c r="S31" t="n">
         <v>93.2</v>
@@ -8972,7 +8972,7 @@
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr"/>
@@ -8989,12 +8989,12 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -9004,127 +9004,127 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Last 7 games: 1/22, 0 HR</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.6% barrel, 12.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 8.6 HR allowed</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>47.45</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>92.04</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>99.2694</t>
+          <t>102.6297</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>0.4342</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>0.1948</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>39.01</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>40.65</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.58</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.2024</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.78</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>0.4158</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.1796</t>
         </is>
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>33.16</t>
         </is>
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr"/>
@@ -9135,32 +9135,32 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>695600</t>
+          <t>802139</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>JJ Wetherholt</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-17T23:40:00Z</t>
+          <t>2026-08-17T22:40:00Z</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -9170,12 +9170,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Mason Barnett</t>
+          <t>Rhett Lowder</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>686930</t>
+          <t>695076</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -9184,7 +9184,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>56.7</v>
+        <v>56.6</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -9198,17 +9198,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>53.4</v>
+        <v>37.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>48.6</v>
+        <v>50.9</v>
       </c>
       <c r="R32" t="n">
-        <v>47.7</v>
+        <v>78.3</v>
       </c>
       <c r="S32" t="n">
         <v>93.2</v>
@@ -9252,7 +9252,7 @@
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr"/>
@@ -9269,12 +9269,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -9284,127 +9284,127 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/22, 0 HR</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 8.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.6% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>EV profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>47.45</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>92.04</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>102.6297</t>
+          <t>99.2694</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>0.4342</t>
+          <t>0.431</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>0.1948</t>
+          <t>0.177</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>39.01</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>29.58</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.2024</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>0.4158</t>
+          <t>0.456</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
-          <t>0.1796</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>33.16</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr"/>
@@ -9695,27 +9695,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>682829</t>
+          <t>683737</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Elly De La Cruz</t>
+          <t>Michael Busch</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-17T22:40:00Z</t>
+          <t>2026-08-18T00:05:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9725,17 +9725,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Andre Pallante</t>
+          <t>Luis Castillo</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>669467</t>
+          <t>622491</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -9758,26 +9758,26 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>55.1</v>
+        <v>43.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>25.8</v>
+        <v>53.1</v>
       </c>
       <c r="R34" t="n">
-        <v>79.3</v>
+        <v>46.3</v>
       </c>
       <c r="S34" t="n">
-        <v>93.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T34" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -9844,127 +9844,127 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/26, 0 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.8% barrel, 13.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.8% barrel, 18.8 HR allowed</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>11.36</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>48.96</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>92.89</t>
+          <t>89.26</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>103.9074</t>
+          <t>99.5152</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.4576</t>
+          <t>0.443</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>0.2013</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.3486</t>
+          <t>0.3444</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>75.38</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>25.24</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.2033</t>
+          <t>0.1773</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>36.26</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>88.01</t>
+          <t>90.16</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0.3817</t>
+          <t>0.4334</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0.1321</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr"/>
@@ -9975,27 +9975,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>683737</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Michael Busch</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-18T00:05:00Z</t>
+          <t>2026-08-18T00:40:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -10005,17 +10005,17 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Luis Castillo</t>
+          <t>Tomoyuki Sugano</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>622491</t>
+          <t>608372</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -10038,26 +10038,26 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Pitcher Vulnerable, Good Environment</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>43.5</v>
+        <v>41</v>
       </c>
       <c r="Q35" t="n">
-        <v>53.1</v>
+        <v>73.3</v>
       </c>
       <c r="R35" t="n">
-        <v>46.3</v>
+        <v>79.7</v>
       </c>
       <c r="S35" t="n">
-        <v>96.59999999999999</v>
+        <v>52.4</v>
       </c>
       <c r="T35" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U35" t="n">
-        <v>23.4</v>
+        <v>21.5</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -10124,127 +10124,127 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 5/19, 0 HR</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.8% barrel, 18.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 13.1% barrel, 26.7 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>11.36</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>44.07</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>89.26</t>
+          <t>89.85</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>99.5152</t>
+          <t>101.0244</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.2013</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.3444</t>
+          <t>0.316</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.1773</t>
+          <t>0.165</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>42.32</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>90.16</t>
+          <t>90.49</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.4334</t>
+          <t>0.552</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.249</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -10255,47 +10255,47 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>682829</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Teoscar Hernández</t>
+          <t>Elly De La Cruz</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-18T00:40:00Z</t>
+          <t>2026-08-17T22:40:00Z</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Tomoyuki Sugano</t>
+          <t>Andre Pallante</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>608372</t>
+          <t>669467</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -10304,7 +10304,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>56</v>
+        <v>55.9</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -10318,26 +10318,26 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable, Good Environment</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>41</v>
+        <v>55.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>73.3</v>
+        <v>25.8</v>
       </c>
       <c r="R36" t="n">
-        <v>79.7</v>
+        <v>78.3</v>
       </c>
       <c r="S36" t="n">
-        <v>52.4</v>
+        <v>93.2</v>
       </c>
       <c r="T36" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U36" t="n">
-        <v>21.5</v>
+        <v>0</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -10404,127 +10404,127 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 0 HR</t>
+          <t>Last 7 games: 2/26, 0 HR</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 13.1% barrel, 26.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.8% barrel, 13.3 HR allowed</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>44.07</t>
+          <t>48.96</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>89.85</t>
+          <t>92.89</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>101.0244</t>
+          <t>103.9074</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.4576</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.194</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>0.3486</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>75.38</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>25.24</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>0.2033</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>90.49</t>
+          <t>88.01</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>0.3817</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>0.1321</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr"/>
@@ -11400,7 +11400,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -11424,7 +11424,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>54.8</v>
+        <v>54.7</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -11448,7 +11448,7 @@
         <v>50.9</v>
       </c>
       <c r="R40" t="n">
-        <v>79.3</v>
+        <v>78.3</v>
       </c>
       <c r="S40" t="n">
         <v>100</v>
@@ -11639,7 +11639,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI40" t="inlineStr">
@@ -14175,27 +14175,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>553993</t>
+          <t>690993</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Eugenio Suárez</t>
+          <t>Colt Keith</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-17T22:40:00Z</t>
+          <t>2026-08-17T23:05:00Z</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -14210,12 +14210,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Andre Pallante</t>
+          <t>Carmen Mlodzinski</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>669467</t>
+          <t>669387</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -14238,26 +14238,26 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="Q50" t="n">
-        <v>27.2</v>
+        <v>41.1</v>
       </c>
       <c r="R50" t="n">
-        <v>79.3</v>
+        <v>62.8</v>
       </c>
       <c r="S50" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T50" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U50" t="n">
-        <v>48.7</v>
+        <v>30.3</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -14309,27 +14309,27 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/15, 1 HR</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.8% barrel, 13.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
@@ -14339,112 +14339,112 @@
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>39.41</t>
+          <t>42.16</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>89.08</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>100.1454</t>
+          <t>100.0111</t>
         </is>
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>0.3804</t>
+          <t>0.4335</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>0.1848</t>
+          <t>0.1646</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr">
         <is>
-          <t>0.2892</t>
+          <t>0.3333</t>
         </is>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>71.95</t>
+          <t>71.47</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>21.04</t>
+          <t>15.43</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>48.87</t>
+          <t>37.03</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>26.79</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>0.2371</t>
+          <t>0.1549</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>36.26</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>88.01</t>
+          <t>90.62</t>
         </is>
       </c>
       <c r="BD50" t="inlineStr">
         <is>
-          <t>0.3817</t>
+          <t>0.4251</t>
         </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
-          <t>0.1321</t>
+          <t>0.1441</t>
         </is>
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="BG50" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI50" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ50" t="inlineStr"/>
@@ -14455,32 +14455,32 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>690993</t>
+          <t>553993</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Colt Keith</t>
+          <t>Eugenio Suárez</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-17T23:05:00Z</t>
+          <t>2026-08-17T22:40:00Z</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -14490,12 +14490,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Carmen Mlodzinski</t>
+          <t>Andre Pallante</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>669387</t>
+          <t>669467</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -14504,7 +14504,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>52.8</v>
+        <v>52.7</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -14518,26 +14518,26 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="Q51" t="n">
-        <v>41.1</v>
+        <v>27.2</v>
       </c>
       <c r="R51" t="n">
-        <v>62.8</v>
+        <v>78.3</v>
       </c>
       <c r="S51" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T51" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U51" t="n">
-        <v>30.3</v>
+        <v>48.7</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
@@ -14589,27 +14589,27 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/15, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL51" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 8.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.8% barrel, 13.3 HR allowed</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
@@ -14619,112 +14619,112 @@
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>42.16</t>
+          <t>39.41</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.08</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>100.0111</t>
+          <t>100.1454</t>
         </is>
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>0.4335</t>
+          <t>0.3804</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>0.1646</t>
+          <t>0.1848</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr">
         <is>
-          <t>0.3333</t>
+          <t>0.2892</t>
         </is>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>71.47</t>
+          <t>71.95</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>15.43</t>
+          <t>21.04</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>48.87</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>26.79</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>0.1549</t>
+          <t>0.2371</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>90.62</t>
+          <t>88.01</t>
         </is>
       </c>
       <c r="BD51" t="inlineStr">
         <is>
-          <t>0.4251</t>
+          <t>0.3817</t>
         </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
-          <t>0.1441</t>
+          <t>0.1321</t>
         </is>
       </c>
       <c r="BF51" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BG51" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI51" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ51" t="inlineStr"/>
@@ -16160,7 +16160,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -16184,7 +16184,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>27.2</v>
       </c>
       <c r="R57" t="n">
-        <v>79.3</v>
+        <v>78.3</v>
       </c>
       <c r="S57" t="n">
         <v>96.59999999999999</v>
@@ -16399,7 +16399,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI57" t="inlineStr">
@@ -16440,7 +16440,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -18960,7 +18960,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -20335,27 +20335,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>691458</t>
+          <t>592518</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Blaze Jordan</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-17T22:40:00Z</t>
+          <t>2026-08-17T23:10:00Z</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -20365,17 +20365,17 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Rhett Lowder</t>
+          <t>Nolan McLean</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>695076</t>
+          <t>690997</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -20398,26 +20398,26 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Good Environment</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>34.4</v>
+        <v>49.8</v>
       </c>
       <c r="Q72" t="n">
-        <v>50.9</v>
+        <v>30.8</v>
       </c>
       <c r="R72" t="n">
-        <v>79.3</v>
+        <v>38.3</v>
       </c>
       <c r="S72" t="n">
-        <v>44.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T72" t="n">
         <v>50</v>
       </c>
       <c r="U72" t="n">
-        <v>39.8</v>
+        <v>13</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
@@ -20452,7 +20452,7 @@
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD72" t="inlineStr"/>
@@ -20469,27 +20469,27 @@
       </c>
       <c r="AH72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 1 HR</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.6% barrel, 12.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.3% barrel, 11.7 HR allowed</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
@@ -20499,112 +20499,112 @@
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>46.95</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>99.9288</t>
+          <t>102.0311</t>
         </is>
       </c>
       <c r="AR72" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>0.4474</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>0.3361</t>
         </is>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>74.64</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>44.37</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>40.78</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>28.01</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.1927</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>38.08</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="BD72" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>0.3514</t>
         </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.1299</t>
         </is>
       </c>
       <c r="BF72" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="BG72" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI72" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ72" t="inlineStr"/>
@@ -20615,47 +20615,47 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>592518</t>
+          <t>691458</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Blaze Jordan</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-17T23:10:00Z</t>
+          <t>2026-08-17T22:40:00Z</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Nolan McLean</t>
+          <t>Rhett Lowder</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>690997</t>
+          <t>695076</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -20664,7 +20664,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -20678,26 +20678,26 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>49.8</v>
+        <v>34.4</v>
       </c>
       <c r="Q73" t="n">
-        <v>30.8</v>
+        <v>50.9</v>
       </c>
       <c r="R73" t="n">
-        <v>38.3</v>
+        <v>78.3</v>
       </c>
       <c r="S73" t="n">
-        <v>96.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="T73" t="n">
         <v>50</v>
       </c>
       <c r="U73" t="n">
-        <v>13</v>
+        <v>39.8</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
@@ -20732,7 +20732,7 @@
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr"/>
@@ -20749,27 +20749,27 @@
       </c>
       <c r="AH73" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 5/19, 1 HR</t>
         </is>
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.3% barrel, 11.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.6% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
@@ -20779,112 +20779,112 @@
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>46.95</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AQ73" t="inlineStr">
         <is>
-          <t>102.0311</t>
+          <t>99.9288</t>
         </is>
       </c>
       <c r="AR73" t="inlineStr">
         <is>
-          <t>0.4474</t>
+          <t>0.418</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr">
         <is>
-          <t>0.3361</t>
+          <t>0.313</t>
         </is>
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>74.64</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>44.37</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>40.78</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>28.01</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>0.1927</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>38.08</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="BD73" t="inlineStr">
         <is>
-          <t>0.3514</t>
+          <t>0.456</t>
         </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
-          <t>0.1299</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BF73" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="BG73" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI73" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ73" t="inlineStr"/>
@@ -20895,22 +20895,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>701675</t>
+          <t>672640</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Nathan Church</t>
+          <t>Otto Lopez</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -20920,27 +20920,27 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Rhett Lowder</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>695076</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L74" t="n">
@@ -20962,22 +20962,22 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>16.4</v>
+        <v>29.8</v>
       </c>
       <c r="Q74" t="n">
-        <v>50.9</v>
+        <v>32.1</v>
       </c>
       <c r="R74" t="n">
-        <v>79.3</v>
+        <v>73.8</v>
       </c>
       <c r="S74" t="n">
-        <v>76.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T74" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U74" t="n">
-        <v>13.6</v>
+        <v>7</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
@@ -20991,7 +20991,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
@@ -21012,7 +21012,7 @@
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD74" t="inlineStr"/>
@@ -21029,12 +21029,12 @@
       </c>
       <c r="AH74" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
@@ -21044,12 +21044,12 @@
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/19, 0 HR</t>
+          <t>Last 7 games: 5/30, 0 HR</t>
         </is>
       </c>
       <c r="AL74" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.6% barrel, 12.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.0% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
@@ -21059,112 +21059,112 @@
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>33.87</t>
+          <t>40.26</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>88.85</t>
         </is>
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>97.8043</t>
+          <t>100.178</t>
         </is>
       </c>
       <c r="AR74" t="inlineStr">
         <is>
-          <t>0.3378</t>
+          <t>0.4228</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>0.1102</t>
+          <t>0.1461</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr">
         <is>
-          <t>0.2757</t>
+          <t>0.3237</t>
         </is>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>71.77</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>23.16</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>35.13</t>
+          <t>32.72</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>21.04</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.1374</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>41.41</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.14</t>
         </is>
       </c>
       <c r="BD74" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>0.3548</t>
         </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.1228</t>
         </is>
       </c>
       <c r="BF74" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="BG74" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>87</t>
         </is>
       </c>
       <c r="BI74" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ74" t="inlineStr"/>
@@ -21175,27 +21175,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>672640</t>
+          <t>650402</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Otto Lopez</t>
+          <t>Gleyber Torres</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-17T22:40:00Z</t>
+          <t>2026-08-17T23:05:00Z</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -21205,26 +21205,26 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Carmen Mlodzinski</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>669387</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -21238,26 +21238,26 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>29.8</v>
+        <v>25.9</v>
       </c>
       <c r="Q75" t="n">
-        <v>32.1</v>
+        <v>41.1</v>
       </c>
       <c r="R75" t="n">
-        <v>73.8</v>
+        <v>62.8</v>
       </c>
       <c r="S75" t="n">
-        <v>86.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T75" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U75" t="n">
-        <v>7</v>
+        <v>52.1</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -21271,7 +21271,7 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
@@ -21309,27 +21309,27 @@
       </c>
       <c r="AH75" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/30, 0 HR</t>
+          <t>Contact streak: 10/29 over last 7 games</t>
         </is>
       </c>
       <c r="AL75" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.0% barrel, 12.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
@@ -21339,97 +21339,97 @@
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>40.26</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>88.85</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AQ75" t="inlineStr">
         <is>
-          <t>100.178</t>
+          <t>97.7198</t>
         </is>
       </c>
       <c r="AR75" t="inlineStr">
         <is>
-          <t>0.4228</t>
+          <t>0.406</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>0.1461</t>
+          <t>0.1496</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr">
         <is>
-          <t>0.3237</t>
+          <t>0.342</t>
         </is>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>71.77</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>23.16</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>32.72</t>
+          <t>26.41</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>0.1374</t>
+          <t>0.1338</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>41.41</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>89.14</t>
+          <t>90.62</t>
         </is>
       </c>
       <c r="BD75" t="inlineStr">
         <is>
-          <t>0.3548</t>
+          <t>0.4251</t>
         </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
-          <t>0.1228</t>
+          <t>0.1441</t>
         </is>
       </c>
       <c r="BF75" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="BG75" t="inlineStr">
@@ -21439,12 +21439,12 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI75" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ75" t="inlineStr"/>
@@ -21455,27 +21455,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>650402</t>
+          <t>664034</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Gleyber Torres</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-17T23:05:00Z</t>
+          <t>2026-08-17T23:10:00Z</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -21485,17 +21485,17 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Carmen Mlodzinski</t>
+          <t>Nolan McLean</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>669387</t>
+          <t>690997</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -21522,22 +21522,22 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>25.9</v>
+        <v>44</v>
       </c>
       <c r="Q76" t="n">
-        <v>41.1</v>
+        <v>30.8</v>
       </c>
       <c r="R76" t="n">
-        <v>62.8</v>
+        <v>38.3</v>
       </c>
       <c r="S76" t="n">
-        <v>93.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T76" t="n">
         <v>50</v>
       </c>
       <c r="U76" t="n">
-        <v>52.1</v>
+        <v>50.3</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
@@ -21589,12 +21589,12 @@
       </c>
       <c r="AH76" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ76" t="inlineStr">
@@ -21604,12 +21604,12 @@
       </c>
       <c r="AK76" t="inlineStr">
         <is>
-          <t>Contact streak: 10/29 over last 7 games</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL76" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 8.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.3% barrel, 11.7 HR allowed</t>
         </is>
       </c>
       <c r="AM76" t="inlineStr">
@@ -21619,112 +21619,112 @@
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>91.46</t>
         </is>
       </c>
       <c r="AQ76" t="inlineStr">
         <is>
-          <t>97.7198</t>
+          <t>101.2591</t>
         </is>
       </c>
       <c r="AR76" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>0.4299</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>0.1496</t>
+          <t>0.1779</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr">
         <is>
-          <t>0.342</t>
+          <t>0.3266</t>
         </is>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>71.77</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>26.41</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>25.18</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>0.1338</t>
+          <t>0.1884</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>38.08</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>90.62</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="BD76" t="inlineStr">
         <is>
-          <t>0.4251</t>
+          <t>0.3514</t>
         </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
-          <t>0.1441</t>
+          <t>0.1299</t>
         </is>
       </c>
       <c r="BF76" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="BG76" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI76" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ76" t="inlineStr"/>
@@ -21735,47 +21735,47 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>664034</t>
+          <t>701675</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Nathan Church</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-17T23:10:00Z</t>
+          <t>2026-08-17T22:40:00Z</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Nolan McLean</t>
+          <t>Rhett Lowder</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>690997</t>
+          <t>695076</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -21784,7 +21784,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -21798,26 +21798,26 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>44</v>
+        <v>16.4</v>
       </c>
       <c r="Q77" t="n">
-        <v>30.8</v>
+        <v>50.9</v>
       </c>
       <c r="R77" t="n">
-        <v>38.3</v>
+        <v>78.3</v>
       </c>
       <c r="S77" t="n">
-        <v>94.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T77" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U77" t="n">
-        <v>50.3</v>
+        <v>13.6</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -21852,7 +21852,7 @@
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr"/>
@@ -21869,27 +21869,27 @@
       </c>
       <c r="AH77" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.3% barrel, 11.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.6% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
@@ -21899,112 +21899,112 @@
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>33.87</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>91.46</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>101.2591</t>
+          <t>97.8043</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>0.4299</t>
+          <t>0.3378</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>0.1779</t>
+          <t>0.1102</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr">
         <is>
-          <t>0.3266</t>
+          <t>0.2757</t>
         </is>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>71.77</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>35.13</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>25.18</t>
+          <t>21.04</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>14.0</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>0.1884</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>38.08</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="BD77" t="inlineStr">
         <is>
-          <t>0.3514</t>
+          <t>0.456</t>
         </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
-          <t>0.1299</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BF77" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="BG77" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI77" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ77" t="inlineStr"/>
@@ -24280,7 +24280,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -25680,7 +25680,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -25704,7 +25704,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -25728,7 +25728,7 @@
         <v>27.2</v>
       </c>
       <c r="R91" t="n">
-        <v>79.3</v>
+        <v>78.3</v>
       </c>
       <c r="S91" t="n">
         <v>76.2</v>
@@ -25919,7 +25919,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI91" t="inlineStr">
@@ -26520,7 +26520,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -27360,7 +27360,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -27615,27 +27615,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>669911</t>
+          <t>701785</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Michael Toglia</t>
+          <t>Kaelen Culpepper</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-17T22:40:00Z</t>
+          <t>2026-08-17T23:40:00Z</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -27645,26 +27645,26 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Andre Pallante</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>669467</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>44.5</v>
+        <v>44.4</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
@@ -27678,26 +27678,26 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>22.6</v>
+        <v>25.5</v>
       </c>
       <c r="Q98" t="n">
-        <v>25.8</v>
+        <v>39</v>
       </c>
       <c r="R98" t="n">
-        <v>79.3</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="S98" t="n">
-        <v>86.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T98" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U98" t="n">
-        <v>2</v>
+        <v>37.8</v>
       </c>
       <c r="V98" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr">
@@ -27732,7 +27732,7 @@
       <c r="AB98" t="inlineStr"/>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD98" t="inlineStr"/>
@@ -27744,132 +27744,132 @@
       </c>
       <c r="AG98" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Last 6 games: 2/15, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL98" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.8% barrel, 13.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>89.69</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="AQ98" t="inlineStr">
         <is>
-          <t>97.4919</t>
+          <t>99.0373</t>
         </is>
       </c>
       <c r="AR98" t="inlineStr">
         <is>
-          <t>0.2467</t>
+          <t>0.296</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
         <is>
-          <t>0.0638</t>
+          <t>0.098</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr">
         <is>
-          <t>0.2248</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>72.84</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>35.62</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>8.42</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>36.26</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>88.01</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="BD98" t="inlineStr">
         <is>
-          <t>0.3817</t>
+          <t>0.4157</t>
         </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
-          <t>0.1321</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="BF98" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>24.27</t>
         </is>
       </c>
       <c r="BG98" t="inlineStr">
@@ -27879,12 +27879,12 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI98" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ98" t="inlineStr"/>
@@ -27895,56 +27895,56 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>701785</t>
+          <t>669911</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Kaelen Culpepper</t>
+          <t>Michael Toglia</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-17T23:40:00Z</t>
+          <t>2026-08-17T22:40:00Z</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Andre Pallante</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>669467</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>44.4</v>
+        <v>44.3</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
@@ -27958,26 +27958,26 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P99" t="n">
-        <v>25.5</v>
+        <v>22.6</v>
       </c>
       <c r="Q99" t="n">
-        <v>39</v>
+        <v>25.8</v>
       </c>
       <c r="R99" t="n">
-        <v>69.59999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="S99" t="n">
-        <v>52.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T99" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U99" t="n">
-        <v>37.8</v>
+        <v>2</v>
       </c>
       <c r="V99" t="inlineStr">
         <is>
@@ -27991,7 +27991,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr">
@@ -28012,7 +28012,7 @@
       <c r="AB99" t="inlineStr"/>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD99" t="inlineStr"/>
@@ -28024,132 +28024,132 @@
       </c>
       <c r="AG99" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 6 games: 2/15, 0 HR</t>
         </is>
       </c>
       <c r="AL99" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 9.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.8% barrel, 13.3 HR allowed</t>
         </is>
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>89.69</t>
         </is>
       </c>
       <c r="AQ99" t="inlineStr">
         <is>
-          <t>99.0373</t>
+          <t>97.4919</t>
         </is>
       </c>
       <c r="AR99" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>0.2467</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>0.0638</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.2248</t>
         </is>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.84</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>35.62</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.107</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.01</t>
         </is>
       </c>
       <c r="BD99" t="inlineStr">
         <is>
-          <t>0.4157</t>
+          <t>0.3817</t>
         </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1321</t>
         </is>
       </c>
       <c r="BF99" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BG99" t="inlineStr">
@@ -28159,12 +28159,12 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI99" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ99" t="inlineStr"/>
@@ -29040,7 +29040,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -29064,7 +29064,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
@@ -29088,7 +29088,7 @@
         <v>50.9</v>
       </c>
       <c r="R103" t="n">
-        <v>79.3</v>
+        <v>78.3</v>
       </c>
       <c r="S103" t="n">
         <v>52.4</v>
@@ -29279,7 +29279,7 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI103" t="inlineStr">
@@ -29600,7 +29600,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -29855,27 +29855,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>691026</t>
+          <t>678882</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Ceddanne Rafaela</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-17T22:40:00Z</t>
+          <t>2026-08-17T23:10:00Z</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -29885,22 +29885,22 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Rhett Lowder</t>
+          <t>Mitch Bratt</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>695076</t>
+          <t>683352</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L106" t="n">
@@ -29918,26 +29918,26 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Good Environment</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P106" t="n">
-        <v>15.7</v>
+        <v>22.5</v>
       </c>
       <c r="Q106" t="n">
-        <v>50.9</v>
+        <v>29.8</v>
       </c>
       <c r="R106" t="n">
-        <v>79.3</v>
+        <v>37.7</v>
       </c>
       <c r="S106" t="n">
-        <v>64.3</v>
+        <v>100</v>
       </c>
       <c r="T106" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U106" t="n">
-        <v>5.1</v>
+        <v>36.5</v>
       </c>
       <c r="V106" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y106" t="inlineStr">
@@ -29989,142 +29989,142 @@
       </c>
       <c r="AH106" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 7/29, 1 HR</t>
         </is>
       </c>
       <c r="AL106" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.6% barrel, 12.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>34.36</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>86.97</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
         <is>
-          <t>98.6673</t>
+          <t>97.8335</t>
         </is>
       </c>
       <c r="AR106" t="inlineStr">
         <is>
-          <t>0.3372</t>
+          <t>0.3775</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>0.0895</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr">
         <is>
-          <t>0.2972</t>
+          <t>0.291</t>
         </is>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>71.17</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>15.77</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>32.11</t>
+          <t>35.78</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>21.32</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>0.1741</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="BD106" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>0.351</t>
         </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="BF106" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="BG106" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI106" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ106" t="inlineStr"/>
@@ -30135,22 +30135,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>678882</t>
+          <t>657757</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ceddanne Rafaela</t>
+          <t>Gavin Sheets</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -30165,22 +30165,22 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Mitch Bratt</t>
+          <t>Nolan McLean</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>683352</t>
+          <t>690997</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L107" t="n">
@@ -30198,26 +30198,26 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P107" t="n">
-        <v>22.5</v>
+        <v>34.6</v>
       </c>
       <c r="Q107" t="n">
-        <v>29.8</v>
+        <v>30.8</v>
       </c>
       <c r="R107" t="n">
-        <v>37.7</v>
+        <v>38.3</v>
       </c>
       <c r="S107" t="n">
-        <v>100</v>
+        <v>64.3</v>
       </c>
       <c r="T107" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U107" t="n">
-        <v>36.5</v>
+        <v>46.8</v>
       </c>
       <c r="V107" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
@@ -30252,7 +30252,7 @@
       <c r="AB107" t="inlineStr"/>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr"/>
@@ -30269,127 +30269,127 @@
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/29, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL107" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 5.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.3% barrel, 11.7 HR allowed</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>34.36</t>
+          <t>41.81</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>86.97</t>
+          <t>88.29</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
         <is>
-          <t>97.8335</t>
+          <t>99.7542</t>
         </is>
       </c>
       <c r="AR107" t="inlineStr">
         <is>
-          <t>0.3775</t>
+          <t>0.4033</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.1641</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>0.3232</t>
         </is>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>74.52</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>47.88</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>35.78</t>
+          <t>39.19</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>0.1741</t>
+          <t>0.1826</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>38.08</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="BD107" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>0.3514</t>
         </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.1299</t>
         </is>
       </c>
       <c r="BF107" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="BG107" t="inlineStr">
@@ -30399,12 +30399,12 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BI107" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ107" t="inlineStr"/>
@@ -30415,27 +30415,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>657757</t>
+          <t>668670</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Gavin Sheets</t>
+          <t>Jake Rogers</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-17T23:10:00Z</t>
+          <t>2026-08-18T00:05:00Z</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -30445,22 +30445,22 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Nolan McLean</t>
+          <t>Shota Imanaga</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>690997</t>
+          <t>684007</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L108" t="n">
@@ -30482,22 +30482,22 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>34.6</v>
+        <v>27.4</v>
       </c>
       <c r="Q108" t="n">
-        <v>30.8</v>
+        <v>53</v>
       </c>
       <c r="R108" t="n">
-        <v>38.3</v>
+        <v>46.3</v>
       </c>
       <c r="S108" t="n">
-        <v>64.3</v>
+        <v>44.8</v>
       </c>
       <c r="T108" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U108" t="n">
-        <v>46.8</v>
+        <v>22</v>
       </c>
       <c r="V108" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr">
@@ -30549,142 +30549,142 @@
       </c>
       <c r="AH108" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/15, 0 HR</t>
         </is>
       </c>
       <c r="AL108" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.3% barrel, 11.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 28.9 HR allowed</t>
         </is>
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>8.36</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>41.81</t>
+          <t>38.17</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>88.29</t>
+          <t>88.31</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
         <is>
-          <t>99.7542</t>
+          <t>98.2593</t>
         </is>
       </c>
       <c r="AR108" t="inlineStr">
         <is>
-          <t>0.4033</t>
+          <t>0.3056</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>0.1641</t>
+          <t>0.1242</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr">
         <is>
-          <t>0.3232</t>
+          <t>0.2677</t>
         </is>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>74.52</t>
+          <t>70.57</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>47.88</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>39.19</t>
+          <t>45.62</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>32.43</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>0.1826</t>
+          <t>0.1411</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>38.08</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="BD108" t="inlineStr">
         <is>
-          <t>0.3514</t>
+          <t>0.4298</t>
         </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
-          <t>0.1299</t>
+          <t>0.1933</t>
         </is>
       </c>
       <c r="BF108" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>34.39</t>
         </is>
       </c>
       <c r="BG108" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI108" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ108" t="inlineStr"/>
@@ -30695,56 +30695,56 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>668670</t>
+          <t>691026</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Jake Rogers</t>
+          <t>Masyn Winn</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-18T00:05:00Z</t>
+          <t>2026-08-17T22:40:00Z</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Shota Imanaga</t>
+          <t>Rhett Lowder</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>684007</t>
+          <t>695076</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="M109" t="inlineStr">
         <is>
@@ -30758,26 +30758,26 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment</t>
         </is>
       </c>
       <c r="P109" t="n">
-        <v>27.4</v>
+        <v>15.7</v>
       </c>
       <c r="Q109" t="n">
-        <v>53</v>
+        <v>50.9</v>
       </c>
       <c r="R109" t="n">
-        <v>46.3</v>
+        <v>78.3</v>
       </c>
       <c r="S109" t="n">
-        <v>44.8</v>
+        <v>64.3</v>
       </c>
       <c r="T109" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U109" t="n">
-        <v>22</v>
+        <v>5.1</v>
       </c>
       <c r="V109" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y109" t="inlineStr">
@@ -30812,7 +30812,7 @@
       <c r="AB109" t="inlineStr"/>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD109" t="inlineStr"/>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ109" t="inlineStr">
@@ -30844,127 +30844,127 @@
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/15, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL109" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 28.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.6% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>38.17</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>88.31</t>
+          <t>88.23</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
         <is>
-          <t>98.2593</t>
+          <t>98.6673</t>
         </is>
       </c>
       <c r="AR109" t="inlineStr">
         <is>
-          <t>0.3056</t>
+          <t>0.3372</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
         <is>
-          <t>0.1242</t>
+          <t>0.0895</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr">
         <is>
-          <t>0.2677</t>
+          <t>0.2972</t>
         </is>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>70.57</t>
+          <t>71.17</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>15.77</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>45.62</t>
+          <t>32.11</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>21.32</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>0.1411</t>
+          <t>0.089</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="BD109" t="inlineStr">
         <is>
-          <t>0.4298</t>
+          <t>0.456</t>
         </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
-          <t>0.1933</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BF109" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="BG109" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI109" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ109" t="inlineStr"/>
@@ -31280,7 +31280,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -32400,7 +32400,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -34895,27 +34895,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>699302</t>
+          <t>661531</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Héctor Rodríguez</t>
+          <t>Brian Serven</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-17T22:40:00Z</t>
+          <t>2026-08-17T23:40:00Z</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -34925,17 +34925,17 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Andre Pallante</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>669467</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -34958,26 +34958,26 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P124" t="n">
-        <v>16.9</v>
+        <v>36.3</v>
       </c>
       <c r="Q124" t="n">
-        <v>27.2</v>
+        <v>37.3</v>
       </c>
       <c r="R124" t="n">
-        <v>79.3</v>
+        <v>47.7</v>
       </c>
       <c r="S124" t="n">
-        <v>64.3</v>
+        <v>44.8</v>
       </c>
       <c r="T124" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U124" t="n">
-        <v>0</v>
+        <v>26.4</v>
       </c>
       <c r="V124" t="inlineStr">
         <is>
@@ -34991,7 +34991,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
@@ -35029,27 +35029,27 @@
       </c>
       <c r="AH124" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/19, 0 HR</t>
+          <t>Last 7 games: 4/23, 1 HR</t>
         </is>
       </c>
       <c r="AL124" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.8% barrel, 13.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 17.1 HR allowed</t>
         </is>
       </c>
       <c r="AM124" t="inlineStr">
@@ -35059,112 +35059,112 @@
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AQ124" t="inlineStr">
         <is>
-          <t>97.8059</t>
+          <t>99.0447</t>
         </is>
       </c>
       <c r="AR124" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.419</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>0.169</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>0.298</t>
         </is>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>0.193</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>36.26</t>
+          <t>35.93</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>88.01</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BD124" t="inlineStr">
         <is>
-          <t>0.3817</t>
+          <t>0.4144</t>
         </is>
       </c>
       <c r="BE124" t="inlineStr">
         <is>
-          <t>0.1321</t>
+          <t>0.1633</t>
         </is>
       </c>
       <c r="BF124" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="BG124" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH124" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>86</t>
         </is>
       </c>
       <c r="BI124" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ124" t="inlineStr"/>
@@ -35175,47 +35175,47 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>661531</t>
+          <t>699302</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brian Serven</t>
+          <t>Héctor Rodríguez</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-17T23:40:00Z</t>
+          <t>2026-08-17T22:40:00Z</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Andre Pallante</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>669467</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -35224,7 +35224,7 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
@@ -35238,26 +35238,26 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P125" t="n">
-        <v>36.3</v>
+        <v>16.9</v>
       </c>
       <c r="Q125" t="n">
-        <v>37.3</v>
+        <v>27.2</v>
       </c>
       <c r="R125" t="n">
-        <v>47.7</v>
+        <v>78.3</v>
       </c>
       <c r="S125" t="n">
-        <v>44.8</v>
+        <v>64.3</v>
       </c>
       <c r="T125" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U125" t="n">
-        <v>26.4</v>
+        <v>0</v>
       </c>
       <c r="V125" t="inlineStr">
         <is>
@@ -35271,7 +35271,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y125" t="inlineStr">
@@ -35309,27 +35309,27 @@
       </c>
       <c r="AH125" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/23, 1 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL125" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 17.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.8% barrel, 13.3 HR allowed</t>
         </is>
       </c>
       <c r="AM125" t="inlineStr">
@@ -35339,112 +35339,112 @@
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AQ125" t="inlineStr">
         <is>
-          <t>99.0447</t>
+          <t>97.8059</t>
         </is>
       </c>
       <c r="AR125" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>0.022</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>0.209</t>
         </is>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>0.042</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>35.93</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>88.01</t>
         </is>
       </c>
       <c r="BD125" t="inlineStr">
         <is>
-          <t>0.4144</t>
+          <t>0.3817</t>
         </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
-          <t>0.1633</t>
+          <t>0.1321</t>
         </is>
       </c>
       <c r="BF125" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BG125" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH125" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI125" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ125" t="inlineStr"/>
@@ -36600,7 +36600,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -37440,7 +37440,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -40520,7 +40520,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -40544,7 +40544,7 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>35.5</v>
+        <v>35.3</v>
       </c>
       <c r="M144" t="inlineStr">
         <is>
@@ -40568,7 +40568,7 @@
         <v>27.2</v>
       </c>
       <c r="R144" t="n">
-        <v>79.3</v>
+        <v>78.3</v>
       </c>
       <c r="S144" t="n">
         <v>52.4</v>
@@ -40759,7 +40759,7 @@
       </c>
       <c r="BH144" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI144" t="inlineStr">
@@ -40775,27 +40775,27 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>670770</t>
+          <t>664983</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>TJ Friedl</t>
+          <t>Jake McCarthy</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-08-17T22:40:00Z</t>
+          <t>2026-08-18T00:40:00Z</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -40805,26 +40805,26 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Andre Pallante</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>669467</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="M145" t="inlineStr">
         <is>
@@ -40838,26 +40838,26 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P145" t="n">
-        <v>9.699999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="Q145" t="n">
-        <v>27.2</v>
+        <v>1.2</v>
       </c>
       <c r="R145" t="n">
-        <v>79.3</v>
+        <v>79.7</v>
       </c>
       <c r="S145" t="n">
-        <v>44.8</v>
+        <v>93.2</v>
       </c>
       <c r="T145" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U145" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V145" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y145" t="inlineStr">
@@ -40909,27 +40909,27 @@
       </c>
       <c r="AH145" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AI145" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/13, 0 HR</t>
+          <t>Last 7 games: 5/28, 0 HR</t>
         </is>
       </c>
       <c r="AL145" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.8% barrel, 13.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.7% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM145" t="inlineStr">
@@ -40939,112 +40939,112 @@
       </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>26.76</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>84.77</t>
         </is>
       </c>
       <c r="AQ145" t="inlineStr">
         <is>
-          <t>97.0489</t>
+          <t>96.5962</t>
         </is>
       </c>
       <c r="AR145" t="inlineStr">
         <is>
-          <t>0.2645</t>
+          <t>0.3971</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>0.0739</t>
+          <t>0.1336</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr">
         <is>
-          <t>0.2538</t>
+          <t>0.3084</t>
         </is>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>70.68</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>11.51</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>37.52</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>25.38</t>
+          <t>21.87</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>0.0918</t>
+          <t>0.1816</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>36.26</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>88.01</t>
+          <t>84.38</t>
         </is>
       </c>
       <c r="BD145" t="inlineStr">
         <is>
-          <t>0.3817</t>
+          <t>0.2793</t>
         </is>
       </c>
       <c r="BE145" t="inlineStr">
         <is>
-          <t>0.1321</t>
+          <t>0.0651</t>
         </is>
       </c>
       <c r="BF145" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BG145" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH145" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI145" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ145" t="inlineStr"/>
@@ -41055,56 +41055,56 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>664983</t>
+          <t>670770</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Jake McCarthy</t>
+          <t>TJ Friedl</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-08-18T00:40:00Z</t>
+          <t>2026-08-17T22:40:00Z</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Andre Pallante</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>669467</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="M146" t="inlineStr">
         <is>
@@ -41118,26 +41118,26 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Good Environment, Premium Lineup Spot</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P146" t="n">
-        <v>14.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q146" t="n">
-        <v>1.2</v>
+        <v>27.2</v>
       </c>
       <c r="R146" t="n">
-        <v>79.7</v>
+        <v>78.3</v>
       </c>
       <c r="S146" t="n">
-        <v>93.2</v>
+        <v>44.8</v>
       </c>
       <c r="T146" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U146" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="V146" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y146" t="inlineStr">
@@ -41189,12 +41189,12 @@
       </c>
       <c r="AH146" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ146" t="inlineStr">
@@ -41204,12 +41204,12 @@
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 0 HR</t>
+          <t>Last 7 games: 0/13, 0 HR</t>
         </is>
       </c>
       <c r="AL146" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.7% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.8% barrel, 13.3 HR allowed</t>
         </is>
       </c>
       <c r="AM146" t="inlineStr">
@@ -41219,112 +41219,112 @@
       </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>26.76</t>
+          <t>28.95</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>84.77</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AQ146" t="inlineStr">
         <is>
-          <t>96.5962</t>
+          <t>97.0489</t>
         </is>
       </c>
       <c r="AR146" t="inlineStr">
         <is>
-          <t>0.3971</t>
+          <t>0.2645</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>0.1336</t>
+          <t>0.0739</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr">
         <is>
-          <t>0.3084</t>
+          <t>0.2538</t>
         </is>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>70.68</t>
+          <t>70.67</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>37.52</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>21.87</t>
+          <t>25.38</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>0.1816</t>
+          <t>0.0918</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>84.38</t>
+          <t>88.01</t>
         </is>
       </c>
       <c r="BD146" t="inlineStr">
         <is>
-          <t>0.2793</t>
+          <t>0.3817</t>
         </is>
       </c>
       <c r="BE146" t="inlineStr">
         <is>
-          <t>0.0651</t>
+          <t>0.1321</t>
         </is>
       </c>
       <c r="BF146" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BG146" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH146" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI146" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ146" t="inlineStr"/>
@@ -44206,7 +44206,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -44230,7 +44230,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>77.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -44254,7 +44254,7 @@
         <v>50.9</v>
       </c>
       <c r="R3" t="n">
-        <v>79.3</v>
+        <v>78.3</v>
       </c>
       <c r="S3" t="n">
         <v>86.40000000000001</v>
@@ -44445,7 +44445,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -44766,7 +44766,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -45606,7 +45606,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -45630,7 +45630,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>67</v>
+        <v>66.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -45654,7 +45654,7 @@
         <v>50.9</v>
       </c>
       <c r="R8" t="n">
-        <v>79.3</v>
+        <v>78.3</v>
       </c>
       <c r="S8" t="n">
         <v>96.59999999999999</v>
@@ -45845,7 +45845,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -47821,27 +47821,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>691023</t>
+          <t>678246</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-17T22:40:00Z</t>
+          <t>2026-08-18T00:05:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -47851,22 +47851,22 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Rhett Lowder</t>
+          <t>Shota Imanaga</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>695076</t>
+          <t>684007</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -47884,26 +47884,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>55.9</v>
+        <v>55.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>50.9</v>
+        <v>53</v>
       </c>
       <c r="R16" t="n">
-        <v>79.3</v>
+        <v>46.3</v>
       </c>
       <c r="S16" t="n">
-        <v>94.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U16" t="n">
-        <v>44.1</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -47917,7 +47917,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -47938,7 +47938,7 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -47955,142 +47955,142 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Hot streak: 4 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.6% barrel, 12.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 28.9 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>48.46</t>
+          <t>44.56</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>92.58</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>104.6627</t>
+          <t>100.4699</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4526</t>
+          <t>0.4861</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1956</t>
+          <t>0.2319</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3347</t>
+          <t>0.3638</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>78.87</t>
+          <t>73.05</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>82.77</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>36.22</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>0.2265</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>0.4298</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.1933</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>34.39</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr"/>
@@ -48101,56 +48101,56 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>678246</t>
+          <t>691023</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-18T00:05:00Z</t>
+          <t>2026-08-17T22:40:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Shota Imanaga</t>
+          <t>Rhett Lowder</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>684007</t>
+          <t>695076</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>62.6</v>
+        <v>62.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -48164,26 +48164,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>55.1</v>
+        <v>55.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>53</v>
+        <v>50.9</v>
       </c>
       <c r="R17" t="n">
-        <v>46.3</v>
+        <v>78.3</v>
       </c>
       <c r="S17" t="n">
-        <v>96.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>83.59999999999999</v>
+        <v>44.1</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -48197,7 +48197,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -48218,7 +48218,7 @@
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -48235,142 +48235,142 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Hot streak: 4 HR in last 7 games</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 28.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.6% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher allows elevated contact</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>44.56</t>
+          <t>48.46</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>92.58</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>100.4699</t>
+          <t>104.6627</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4861</t>
+          <t>0.4526</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.2319</t>
+          <t>0.1956</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3638</t>
+          <t>0.3347</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>73.05</t>
+          <t>78.87</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>82.77</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>37.96</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>36.22</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.2265</t>
+          <t>0.175</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.4298</t>
+          <t>0.456</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1933</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr"/>
@@ -48966,7 +48966,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-17.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-17.xlsx
@@ -7200,7 +7200,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -12240,7 +12240,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -14760,7 +14760,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -16160,7 +16160,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -16511,7 +16511,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
@@ -16521,7 +16521,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -16529,11 +16529,7 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>order MLB 2 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -17284,7 +17280,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -18684,7 +18680,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -22044,7 +22040,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -23724,7 +23720,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -26524,7 +26520,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -27924,7 +27920,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -29044,7 +29040,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -29604,7 +29600,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -30235,7 +30231,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
@@ -30245,7 +30241,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -30253,11 +30249,7 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>order MLB 6 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB107" t="inlineStr"/>
       <c r="AC107" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -31568,7 +31560,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -33312,28 +33304,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W118" t="inlineStr"/>
-      <c r="X118" t="inlineStr"/>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y118" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB118" t="inlineStr"/>
       <c r="AC118" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>

--- a/outputs/daily/hr_rankings_2026-08-17.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-17.xlsx
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>68.09999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>53</v>
       </c>
       <c r="R4" t="n">
-        <v>46.3</v>
+        <v>40.3</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -1855,32 +1855,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>678246</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-18T00:05:00Z</t>
+          <t>2026-08-18T00:40:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1890,21 +1890,21 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Shota Imanaga</t>
+          <t>Tomoyuki Sugano</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>684007</t>
+          <t>608372</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>62.6</v>
+        <v>62.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1918,26 +1918,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Pitcher Vulnerable, Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>55.1</v>
+        <v>36.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>53</v>
+        <v>73.3</v>
       </c>
       <c r="R6" t="n">
-        <v>46.3</v>
+        <v>79.7</v>
       </c>
       <c r="S6" t="n">
         <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>83.59999999999999</v>
+        <v>53.3</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1989,142 +1989,142 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 4 HR in last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 28.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 13.1% barrel, 26.7 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>44.56</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>88.81</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.4699</t>
+          <t>99.8166</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4861</t>
+          <t>0.4343</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2319</t>
+          <t>0.1693</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3638</t>
+          <t>0.3307</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.05</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>37.97</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>36.22</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.2265</t>
+          <t>0.1897</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>42.32</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>90.49</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.4298</t>
+          <t>0.552</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1933</t>
+          <t>0.249</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr"/>
@@ -2135,24 +2135,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>691182</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Adael Amador</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-08-18T00:40:00Z</t>
@@ -2165,26 +2165,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Tomoyuki Sugano</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>608372</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>62.2</v>
+        <v>62</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2198,26 +2198,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable, Good Environment, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.3</v>
+        <v>93.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>73.3</v>
+        <v>1.1</v>
       </c>
       <c r="R7" t="n">
         <v>79.7</v>
       </c>
       <c r="S7" t="n">
-        <v>96.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U7" t="n">
-        <v>53.3</v>
+        <v>63.3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2264,132 +2264,132 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 1/2 over last 2 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 13.1% barrel, 26.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.7% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>71.02</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>77.41</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>88.81</t>
+          <t>97.05</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>99.8166</t>
+          <t>100.4977</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4343</t>
+          <t>0.6154</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1693</t>
+          <t>0.4065</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3307</t>
+          <t>0.4601</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>70.39</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>82.48</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1897</t>
+          <t>1.0764</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>90.49</t>
+          <t>84.38</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>0.2793</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>0.0651</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -2415,47 +2415,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>691182</t>
+          <t>678246</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Adael Amador</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-18T00:40:00Z</t>
+          <t>2026-08-18T00:05:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Shota Imanaga</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>684007</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>62</v>
+        <v>61.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2478,26 +2478,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Good Environment, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>93.5</v>
+        <v>55.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.1</v>
+        <v>53</v>
       </c>
       <c r="R8" t="n">
-        <v>79.7</v>
+        <v>40.3</v>
       </c>
       <c r="S8" t="n">
-        <v>64.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U8" t="n">
-        <v>63.3</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2544,147 +2544,147 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Contact streak: 1/2 over last 2 games</t>
+          <t>Hot streak: 4 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.7% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 28.9 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>71.02</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>77.41</t>
+          <t>44.56</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>97.05</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.4977</t>
+          <t>100.4699</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.6154</t>
+          <t>0.4861</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.4065</t>
+          <t>0.2319</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4601</t>
+          <t>0.3638</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>70.39</t>
+          <t>73.05</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>82.48</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>36.22</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1.0764</t>
+          <t>0.2265</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>84.38</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.2793</t>
+          <t>0.4298</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.0651</t>
+          <t>0.1933</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>34.39</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr"/>
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>59.5</v>
+        <v>58.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>53.1</v>
       </c>
       <c r="R10" t="n">
-        <v>46.3</v>
+        <v>40.3</v>
       </c>
       <c r="S10" t="n">
         <v>93.2</v>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3255,56 +3255,56 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>545341</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Randal Grichuk</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-18T00:05:00Z</t>
+          <t>2026-08-18T00:40:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Shota Imanaga</t>
+          <t>Tomoyuki Sugano</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>684007</t>
+          <t>608372</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>59.2</v>
+        <v>58.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3318,26 +3318,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Pitcher Vulnerable, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>51.7</v>
+        <v>33.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>53</v>
+        <v>73.3</v>
       </c>
       <c r="R11" t="n">
-        <v>46.3</v>
+        <v>79.7</v>
       </c>
       <c r="S11" t="n">
-        <v>94.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>43.8</v>
+        <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -3389,12 +3389,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3404,12 +3404,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Contact streak: 7/17 over last 7 games</t>
+          <t>Last 7 games: 1/23, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 28.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 13.1% barrel, 26.7 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3419,112 +3419,112 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>48.59</t>
+          <t>38.58</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>91.56</t>
+          <t>89.12</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>103.0646</t>
+          <t>98.8499</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4724</t>
+          <t>0.4165</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>0.1549</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3344</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>71.51</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>43.17</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>43.66</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>27.52</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.2332</t>
+          <t>0.156</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>42.32</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>90.49</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.4298</t>
+          <t>0.552</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1933</t>
+          <t>0.249</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr"/>
@@ -3535,56 +3535,56 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>545341</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Randal Grichuk</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-18T00:40:00Z</t>
+          <t>2026-08-18T00:05:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Tomoyuki Sugano</t>
+          <t>Shota Imanaga</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>608372</t>
+          <t>684007</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>58.5</v>
+        <v>58.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3598,26 +3598,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable, Good Environment, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>33.5</v>
+        <v>51.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>73.3</v>
+        <v>53</v>
       </c>
       <c r="R12" t="n">
-        <v>79.7</v>
+        <v>40.3</v>
       </c>
       <c r="S12" t="n">
-        <v>76.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>43.8</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -3669,12 +3669,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/23, 0 HR</t>
+          <t>Contact streak: 7/17 over last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 13.1% barrel, 26.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 28.9 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3699,112 +3699,112 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>48.59</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.12</t>
+          <t>91.56</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>98.8499</t>
+          <t>103.0646</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4165</t>
+          <t>0.4724</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1549</t>
+          <t>0.197</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.3344</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>71.51</t>
+          <t>74.18</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>43.17</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>43.66</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>27.52</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>0.2332</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>90.49</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>0.4298</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>0.1933</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>34.39</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -3864,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>56.9</v>
+        <v>56</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>53.1</v>
       </c>
       <c r="R13" t="n">
-        <v>46.3</v>
+        <v>40.3</v>
       </c>
       <c r="S13" t="n">
         <v>100</v>
@@ -4074,12 +4074,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4095,47 +4095,47 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>683737</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Michael Busch</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-18T00:05:00Z</t>
+          <t>2026-08-18T00:40:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Luis Castillo</t>
+          <t>Tomoyuki Sugano</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>622491</t>
+          <t>608372</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4158,26 +4158,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Pitcher Vulnerable, Good Environment</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>43.5</v>
+        <v>41</v>
       </c>
       <c r="Q14" t="n">
-        <v>53.1</v>
+        <v>73.3</v>
       </c>
       <c r="R14" t="n">
-        <v>46.3</v>
+        <v>79.7</v>
       </c>
       <c r="S14" t="n">
-        <v>96.59999999999999</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>23.4</v>
+        <v>21.5</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -4244,127 +4244,127 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 5/19, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.8% barrel, 18.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 13.1% barrel, 26.7 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>11.36</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>44.07</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>89.26</t>
+          <t>89.85</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>99.5152</t>
+          <t>101.0244</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.2013</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3444</t>
+          <t>0.316</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1773</t>
+          <t>0.165</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>42.32</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>90.16</t>
+          <t>90.49</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.4334</t>
+          <t>0.552</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.249</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>676439</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Teoscar Hernández</t>
+          <t>Hunter Feduccia</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -4424,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>56</v>
+        <v>55.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4438,11 +4438,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable, Good Environment</t>
+          <t>Pitcher Vulnerable, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="Q15" t="n">
         <v>73.3</v>
@@ -4451,13 +4451,13 @@
         <v>79.7</v>
       </c>
       <c r="S15" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>21.5</v>
+        <v>43.2</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -4509,27 +4509,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 0 HR</t>
+          <t>Last 7 games: 4/14, 1 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 13.1% barrel, 26.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 13.1% barrel, 26.7 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4539,67 +4539,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>44.07</t>
+          <t>37.84</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>89.85</t>
+          <t>89.56</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>101.0244</t>
+          <t>99.1664</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.3664</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.1325</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>0.3065</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>70.78</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>32.38</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>0.099</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -4655,47 +4655,47 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>676439</t>
+          <t>683737</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hunter Feduccia</t>
+          <t>Michael Busch</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-18T00:40:00Z</t>
+          <t>2026-08-18T00:05:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Tomoyuki Sugano</t>
+          <t>Luis Castillo</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>608372</t>
+          <t>622491</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>55.4</v>
+        <v>55.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4718,26 +4718,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable, Good Environment, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>31</v>
+        <v>43.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>73.3</v>
+        <v>53.1</v>
       </c>
       <c r="R16" t="n">
-        <v>79.7</v>
+        <v>40.3</v>
       </c>
       <c r="S16" t="n">
-        <v>44.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>43.2</v>
+        <v>23.4</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -4789,142 +4789,142 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/14, 1 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 13.1% barrel, 26.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.8% barrel, 18.8 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>11.36</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>37.84</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>89.56</t>
+          <t>89.26</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.1664</t>
+          <t>99.5152</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3664</t>
+          <t>0.443</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1325</t>
+          <t>0.2013</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3065</t>
+          <t>0.3444</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>70.78</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>0.1773</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>90.49</t>
+          <t>90.16</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>0.4334</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr"/>
@@ -4935,47 +4935,47 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>664023</t>
+          <t>669242</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ian Happ</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-18T00:05:00Z</t>
+          <t>2026-08-18T00:40:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Luis Castillo</t>
+          <t>Tomoyuki Sugano</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>622491</t>
+          <t>608372</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>54.3</v>
+        <v>54.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4998,26 +4998,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Pitcher Vulnerable, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>43.1</v>
+        <v>23.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>51.1</v>
+        <v>72.2</v>
       </c>
       <c r="R17" t="n">
-        <v>46.3</v>
+        <v>79.7</v>
       </c>
       <c r="S17" t="n">
-        <v>86.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
         <v>75</v>
       </c>
       <c r="U17" t="n">
-        <v>39.5</v>
+        <v>27.6</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5084,127 +5084,127 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 1 HR</t>
+          <t>Last 7 games: 4/22, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.8% barrel, 18.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 13.1% barrel, 26.7 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>10.82</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>42.72</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>89.44</t>
+          <t>88.23</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>100.83</t>
+          <t>99.3821</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>0.3844</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1916</t>
+          <t>0.1202</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3225</t>
+          <t>0.3161</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>71.88</t>
+          <t>70.52</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>12.32</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>41.97</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>26.08</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1903</t>
+          <t>0.1423</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>42.32</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>90.16</t>
+          <t>90.49</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.4334</t>
+          <t>0.552</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.249</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr"/>
@@ -5215,47 +5215,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>664023</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Ian Happ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-18T00:40:00Z</t>
+          <t>2026-08-18T00:05:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Tomoyuki Sugano</t>
+          <t>Luis Castillo</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>608372</t>
+          <t>622491</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>54.2</v>
+        <v>53.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5278,26 +5278,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable, Good Environment, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>23.6</v>
+        <v>43.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>72.2</v>
+        <v>51.1</v>
       </c>
       <c r="R18" t="n">
-        <v>79.7</v>
+        <v>40.3</v>
       </c>
       <c r="S18" t="n">
-        <v>64.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T18" t="n">
         <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>27.6</v>
+        <v>39.5</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5364,127 +5364,127 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 1 HR</t>
+          <t>Last 7 games: 6/23, 1 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 13.1% barrel, 26.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.8% barrel, 18.8 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>10.82</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>42.72</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>89.44</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>99.3821</t>
+          <t>100.83</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3844</t>
+          <t>0.408</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1202</t>
+          <t>0.1916</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3161</t>
+          <t>0.3225</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>70.52</t>
+          <t>71.88</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>41.97</t>
+          <t>43.77</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>26.08</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1423</t>
+          <t>0.1903</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>90.49</t>
+          <t>90.16</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>0.4334</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr"/>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>51.5</v>
+        <v>50.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>53.1</v>
       </c>
       <c r="R19" t="n">
-        <v>46.3</v>
+        <v>40.3</v>
       </c>
       <c r="S19" t="n">
         <v>52.4</v>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -5824,7 +5824,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>50.5</v>
+        <v>49.6</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>53.1</v>
       </c>
       <c r="R20" t="n">
-        <v>46.3</v>
+        <v>40.3</v>
       </c>
       <c r="S20" t="n">
         <v>94.90000000000001</v>
@@ -6034,12 +6034,12 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>47</v>
+        <v>46.1</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>53</v>
       </c>
       <c r="R21" t="n">
-        <v>46.3</v>
+        <v>40.3</v>
       </c>
       <c r="S21" t="n">
         <v>76.2</v>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>46.8</v>
+        <v>45.9</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>52.1</v>
       </c>
       <c r="R22" t="n">
-        <v>46.3</v>
+        <v>40.3</v>
       </c>
       <c r="S22" t="n">
         <v>86.40000000000001</v>
@@ -6594,12 +6594,12 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -6664,7 +6664,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>46.5</v>
+        <v>45.6</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>53</v>
       </c>
       <c r="R23" t="n">
-        <v>46.3</v>
+        <v>40.3</v>
       </c>
       <c r="S23" t="n">
         <v>93.2</v>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -6895,56 +6895,56 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>699393</t>
+          <t>650489</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pedro Ramírez</t>
+          <t>Willi Castro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-18T00:05:00Z</t>
+          <t>2026-08-18T00:40:00Z</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Luis Castillo</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>622491</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>44.2</v>
+        <v>43.5</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6958,26 +6958,26 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>20.2</v>
+        <v>31.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>51.1</v>
+        <v>1.1</v>
       </c>
       <c r="R24" t="n">
-        <v>46.3</v>
+        <v>79.7</v>
       </c>
       <c r="S24" t="n">
-        <v>64.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T24" t="n">
         <v>75</v>
       </c>
       <c r="U24" t="n">
-        <v>50.3</v>
+        <v>18</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -7012,7 +7012,7 @@
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr"/>
@@ -7029,27 +7029,27 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Contact streak: 7/21 over last 7 games</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.8% barrel, 18.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.7% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
@@ -7059,112 +7059,112 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>39.61</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>87.47</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>99.6133</t>
+          <t>100.1299</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>0.3862</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>0.1533</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>0.3067</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.51</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>26.04</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>42.39</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>31.18</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>0.1512</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>90.16</t>
+          <t>84.38</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>0.4334</t>
+          <t>0.2793</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.0651</t>
         </is>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr"/>
@@ -7175,56 +7175,56 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>650489</t>
+          <t>699393</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Willi Castro</t>
+          <t>Pedro Ramírez</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-18T00:40:00Z</t>
+          <t>2026-08-18T00:05:00Z</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Luis Castillo</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>622491</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>43.5</v>
+        <v>43.3</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -7238,26 +7238,26 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>31.4</v>
+        <v>20.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.1</v>
+        <v>51.1</v>
       </c>
       <c r="R25" t="n">
-        <v>79.7</v>
+        <v>40.3</v>
       </c>
       <c r="S25" t="n">
-        <v>94.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T25" t="n">
         <v>75</v>
       </c>
       <c r="U25" t="n">
-        <v>18</v>
+        <v>50.3</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -7292,7 +7292,7 @@
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr"/>
@@ -7309,27 +7309,27 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Contact streak: 7/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.7% barrel, 0.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.8% barrel, 18.8 HR allowed</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
@@ -7339,112 +7339,112 @@
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>39.61</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>87.47</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>100.1299</t>
+          <t>99.6133</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>0.3862</t>
+          <t>0.354</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>0.1533</t>
+          <t>0.089</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>0.3067</t>
+          <t>0.297</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>72.51</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>26.04</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>42.39</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>17.6</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>0.1512</t>
+          <t>0.142</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>84.38</t>
+          <t>90.16</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>0.2793</t>
+          <t>0.4334</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
-          <t>0.0651</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr"/>
@@ -7455,47 +7455,47 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>668670</t>
+          <t>664954</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jake Rogers</t>
+          <t>Brett Sullivan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-18T00:05:00Z</t>
+          <t>2026-08-18T00:40:00Z</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Shota Imanaga</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>684007</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -7504,7 +7504,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>43.1</v>
+        <v>42.8</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7518,26 +7518,26 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel, Good Environment, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>27.4</v>
+        <v>44</v>
       </c>
       <c r="Q26" t="n">
-        <v>53</v>
+        <v>1.2</v>
       </c>
       <c r="R26" t="n">
-        <v>46.3</v>
+        <v>79.7</v>
       </c>
       <c r="S26" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T26" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U26" t="n">
-        <v>22</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -7589,142 +7589,142 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/15, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 28.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.7% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>38.17</t>
+          <t>52.96</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>88.31</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>98.2593</t>
+          <t>97.913</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>0.3056</t>
+          <t>0.3652</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>0.1242</t>
+          <t>0.164</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>0.2677</t>
+          <t>0.3068</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>70.57</t>
+          <t>68.81</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>45.62</t>
+          <t>53.15</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>35.93</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.1411</t>
+          <t>0.147</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>84.38</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>0.4298</t>
+          <t>0.2793</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>0.1933</t>
+          <t>0.0651</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr"/>
@@ -7735,47 +7735,47 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>664954</t>
+          <t>668670</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brett Sullivan</t>
+          <t>Jake Rogers</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-18T00:40:00Z</t>
+          <t>2026-08-18T00:05:00Z</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Shota Imanaga</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>684007</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -7784,7 +7784,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>42.8</v>
+        <v>42.2</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7798,26 +7798,26 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Strong Barrel, Good Environment, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>44</v>
+        <v>27.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.2</v>
+        <v>53</v>
       </c>
       <c r="R27" t="n">
-        <v>79.7</v>
+        <v>40.3</v>
       </c>
       <c r="S27" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T27" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U27" t="n">
-        <v>84.40000000000001</v>
+        <v>22</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -7869,142 +7869,142 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 4/15, 0 HR</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.7% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 28.9 HR allowed</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>10.65</t>
+          <t>8.36</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>52.96</t>
+          <t>38.17</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>88.31</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>97.913</t>
+          <t>98.2593</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>0.3652</t>
+          <t>0.3056</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0.1242</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>0.3068</t>
+          <t>0.2677</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>68.81</t>
+          <t>70.57</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.93</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>53.15</t>
+          <t>45.62</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>35.93</t>
+          <t>32.43</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>0.1411</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>84.38</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>0.2793</t>
+          <t>0.4298</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
-          <t>0.0651</t>
+          <t>0.1933</t>
         </is>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>34.39</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr"/>
@@ -8015,47 +8015,47 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>803011</t>
+          <t>687597</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Jordan Beck</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-18T00:05:00Z</t>
+          <t>2026-08-18T00:40:00Z</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Shota Imanaga</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>684007</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -8064,7 +8064,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>41.5</v>
+        <v>41.2</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -8078,26 +8078,26 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>53</v>
+        <v>1.2</v>
       </c>
       <c r="R28" t="n">
-        <v>46.3</v>
+        <v>79.7</v>
       </c>
       <c r="S28" t="n">
-        <v>64.3</v>
+        <v>100</v>
       </c>
       <c r="T28" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U28" t="n">
-        <v>25.8</v>
+        <v>17.7</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -8132,7 +8132,7 @@
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr"/>
@@ -8149,12 +8149,12 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -8164,127 +8164,127 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 0 HR</t>
+          <t>Last 7 games: 5/21, 0 HR</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.3% barrel, 28.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 1.7% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>86.84</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>97.9432</t>
+          <t>98.6039</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>0.3341</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.1136</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.2716</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>73.55</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>35.92</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>39.17</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>26.85</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.1426</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>84.38</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>0.4298</t>
+          <t>0.2793</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
-          <t>0.1933</t>
+          <t>0.0651</t>
         </is>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr"/>
@@ -8295,12 +8295,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>687597</t>
+          <t>694249</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jordan Beck</t>
+          <t>Cole Carrigg</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>41.2</v>
+        <v>40.9</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -8362,22 +8362,22 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>21.3</v>
+        <v>22.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="R29" t="n">
         <v>79.7</v>
       </c>
       <c r="S29" t="n">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T29" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U29" t="n">
-        <v>17.7</v>
+        <v>21.1</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -8412,7 +8412,7 @@
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr"/>
@@ -8429,12 +8429,12 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -8444,12 +8444,12 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 0 HR</t>
+          <t>Last 7 games: 6/23, 0 HR</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 1.7% barrel, 0.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.7% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -8459,67 +8459,67 @@
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>32.34</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>86.84</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>98.6039</t>
+          <t>98.1473</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>0.3341</t>
+          <t>0.399</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>0.1136</t>
+          <t>0.134</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>0.2716</t>
+          <t>0.335</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>73.55</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>39.17</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>26.85</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>0.1426</t>
+          <t>0.194</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
@@ -8575,47 +8575,47 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>694249</t>
+          <t>803011</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cole Carrigg</t>
+          <t>Sam Antonacci</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-18T00:40:00Z</t>
+          <t>2026-08-18T00:05:00Z</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Shota Imanaga</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>684007</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -8624,7 +8624,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>40.9</v>
+        <v>40.6</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8638,26 +8638,26 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>22.2</v>
+        <v>21.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.1</v>
+        <v>53</v>
       </c>
       <c r="R30" t="n">
-        <v>79.7</v>
+        <v>40.3</v>
       </c>
       <c r="S30" t="n">
-        <v>96.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T30" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U30" t="n">
-        <v>21.1</v>
+        <v>25.8</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -8724,127 +8724,127 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 0 HR</t>
+          <t>Last 7 games: 7/24, 0 HR</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.7% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.3% barrel, 28.9 HR allowed</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>98.1473</t>
+          <t>97.9432</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>0.406</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>34.1</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>0.129</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>84.38</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>0.2793</t>
+          <t>0.4298</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>0.0651</t>
+          <t>0.1933</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>34.39</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr"/>
@@ -8904,7 +8904,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>40.3</v>
+        <v>39.4</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>53.1</v>
       </c>
       <c r="R31" t="n">
-        <v>46.3</v>
+        <v>40.3</v>
       </c>
       <c r="S31" t="n">
         <v>44.8</v>
@@ -9114,12 +9114,12 @@
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -9135,47 +9135,47 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>682668</t>
+          <t>681393</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Luisangel Acuña</t>
+          <t>Connor Norby</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-18T00:05:00Z</t>
+          <t>2026-08-18T00:40:00Z</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Shota Imanaga</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>684007</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -9184,7 +9184,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>39.6</v>
+        <v>39.4</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -9198,26 +9198,26 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>14.2</v>
+        <v>28.6</v>
       </c>
       <c r="Q32" t="n">
-        <v>53</v>
+        <v>1.2</v>
       </c>
       <c r="R32" t="n">
-        <v>46.3</v>
+        <v>79.7</v>
       </c>
       <c r="S32" t="n">
-        <v>52.4</v>
+        <v>76.2</v>
       </c>
       <c r="T32" t="n">
         <v>78</v>
       </c>
       <c r="U32" t="n">
-        <v>17.3</v>
+        <v>0</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
@@ -9284,127 +9284,127 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 2/17, 0 HR</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 28.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 1.7% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>7.86</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>36.97</t>
+          <t>36.82</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>88.39</t>
+          <t>87.46</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>99.5893</t>
+          <t>97.8306</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>0.3123</t>
+          <t>0.354</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>0.0679</t>
+          <t>0.1501</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>0.2668</t>
+          <t>0.2937</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>71.61</t>
+          <t>70.14</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>7.08</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>32.22</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>16.09</t>
+          <t>34.93</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.0351</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>84.38</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>0.4298</t>
+          <t>0.2793</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
-          <t>0.1933</t>
+          <t>0.0651</t>
         </is>
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr"/>
@@ -9415,47 +9415,47 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>681393</t>
+          <t>682668</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Connor Norby</t>
+          <t>Luisangel Acuña</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-18T00:40:00Z</t>
+          <t>2026-08-18T00:05:00Z</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Shota Imanaga</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>684007</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -9464,7 +9464,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>39.4</v>
+        <v>38.7</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -9478,26 +9478,26 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>28.6</v>
+        <v>14.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.2</v>
+        <v>53</v>
       </c>
       <c r="R33" t="n">
-        <v>79.7</v>
+        <v>40.3</v>
       </c>
       <c r="S33" t="n">
-        <v>76.2</v>
+        <v>52.4</v>
       </c>
       <c r="T33" t="n">
         <v>78</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>17.3</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
@@ -9564,127 +9564,127 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 1.7% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 28.9 HR allowed</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>7.86</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>36.82</t>
+          <t>36.97</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>87.46</t>
+          <t>88.39</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>97.8306</t>
+          <t>99.5893</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>0.3123</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>0.1501</t>
+          <t>0.0679</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>0.2937</t>
+          <t>0.2668</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>70.14</t>
+          <t>71.61</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>7.08</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>32.22</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>34.93</t>
+          <t>16.09</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.0351</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>84.38</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>0.2793</t>
+          <t>0.4298</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>0.0651</t>
+          <t>0.1933</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>34.39</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr"/>
@@ -9744,7 +9744,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>39</v>
+        <v>38.1</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>53.1</v>
       </c>
       <c r="R34" t="n">
-        <v>46.3</v>
+        <v>40.3</v>
       </c>
       <c r="S34" t="n">
         <v>76.2</v>
@@ -9954,12 +9954,12 @@
       </c>
       <c r="BG34" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -11750,7 +11750,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>68.09999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>53</v>
       </c>
       <c r="R4" t="n">
-        <v>46.3</v>
+        <v>40.3</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -11960,12 +11960,12 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -12261,32 +12261,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>678246</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-18T00:05:00Z</t>
+          <t>2026-08-18T00:40:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -12296,21 +12296,21 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Shota Imanaga</t>
+          <t>Tomoyuki Sugano</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>684007</t>
+          <t>608372</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>62.6</v>
+        <v>62.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -12324,26 +12324,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Pitcher Vulnerable, Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>55.1</v>
+        <v>36.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>53</v>
+        <v>73.3</v>
       </c>
       <c r="R6" t="n">
-        <v>46.3</v>
+        <v>79.7</v>
       </c>
       <c r="S6" t="n">
         <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>83.59999999999999</v>
+        <v>53.3</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -12395,142 +12395,142 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 4 HR in last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 28.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 13.1% barrel, 26.7 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>44.56</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>88.81</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.4699</t>
+          <t>99.8166</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4861</t>
+          <t>0.4343</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2319</t>
+          <t>0.1693</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3638</t>
+          <t>0.3307</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.05</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>37.97</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>36.22</t>
+          <t>28.65</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.2265</t>
+          <t>0.1897</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>42.32</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>90.49</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.4298</t>
+          <t>0.552</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1933</t>
+          <t>0.249</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr"/>
@@ -12541,24 +12541,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>691182</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Adael Amador</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-08-18T00:40:00Z</t>
@@ -12571,26 +12571,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Tomoyuki Sugano</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>608372</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>62.2</v>
+        <v>62</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -12604,26 +12604,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable, Good Environment, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>36.3</v>
+        <v>93.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>73.3</v>
+        <v>1.1</v>
       </c>
       <c r="R7" t="n">
         <v>79.7</v>
       </c>
       <c r="S7" t="n">
-        <v>96.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U7" t="n">
-        <v>53.3</v>
+        <v>63.3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -12637,7 +12637,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -12670,132 +12670,132 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 1/2 over last 2 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 13.1% barrel, 26.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.7% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>71.02</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>77.41</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>88.81</t>
+          <t>97.05</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>99.8166</t>
+          <t>100.4977</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4343</t>
+          <t>0.6154</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1693</t>
+          <t>0.4065</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3307</t>
+          <t>0.4601</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>70.39</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>82.48</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1897</t>
+          <t>1.0764</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>90.49</t>
+          <t>84.38</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>0.2793</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>0.0651</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
@@ -12821,47 +12821,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>691182</t>
+          <t>678246</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Adael Amador</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-18T00:40:00Z</t>
+          <t>2026-08-18T00:05:00Z</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Shota Imanaga</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>684007</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -12870,7 +12870,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>62</v>
+        <v>61.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -12884,26 +12884,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel, Good Environment, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>93.5</v>
+        <v>55.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.1</v>
+        <v>53</v>
       </c>
       <c r="R8" t="n">
-        <v>79.7</v>
+        <v>40.3</v>
       </c>
       <c r="S8" t="n">
-        <v>64.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U8" t="n">
-        <v>63.3</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -12950,147 +12950,147 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Contact streak: 1/2 over last 2 games</t>
+          <t>Hot streak: 4 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.7% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 28.9 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>71.02</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>77.41</t>
+          <t>44.56</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>97.05</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.4977</t>
+          <t>100.4699</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.6154</t>
+          <t>0.4861</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.4065</t>
+          <t>0.2319</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4601</t>
+          <t>0.3638</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>70.39</t>
+          <t>73.05</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>82.48</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>36.22</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>1.0764</t>
+          <t>0.2265</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>84.38</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.2793</t>
+          <t>0.4298</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.0651</t>
+          <t>0.1933</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>34.39</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr"/>
@@ -13430,7 +13430,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>59.5</v>
+        <v>58.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>53.1</v>
       </c>
       <c r="R10" t="n">
-        <v>46.3</v>
+        <v>40.3</v>
       </c>
       <c r="S10" t="n">
         <v>93.2</v>
@@ -13640,12 +13640,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -13661,56 +13661,56 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>545341</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Randal Grichuk</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-18T00:05:00Z</t>
+          <t>2026-08-18T00:40:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Shota Imanaga</t>
+          <t>Tomoyuki Sugano</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>684007</t>
+          <t>608372</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>59.2</v>
+        <v>58.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -13724,26 +13724,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Pitcher Vulnerable, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>51.7</v>
+        <v>33.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>53</v>
+        <v>73.3</v>
       </c>
       <c r="R11" t="n">
-        <v>46.3</v>
+        <v>79.7</v>
       </c>
       <c r="S11" t="n">
-        <v>94.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>43.8</v>
+        <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -13795,12 +13795,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -13810,12 +13810,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Contact streak: 7/17 over last 7 games</t>
+          <t>Last 7 games: 1/23, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 28.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 13.1% barrel, 26.7 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -13825,112 +13825,112 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>48.59</t>
+          <t>38.58</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>91.56</t>
+          <t>89.12</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>103.0646</t>
+          <t>98.8499</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4724</t>
+          <t>0.4165</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>0.1549</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3344</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>71.51</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>43.17</t>
+          <t>20.8</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>43.66</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>27.52</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.2332</t>
+          <t>0.156</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>37.9</t>
+          <t>42.32</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>89.02</t>
+          <t>90.49</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.4298</t>
+          <t>0.552</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1933</t>
+          <t>0.249</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr"/>
@@ -13941,56 +13941,56 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>545341</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Randal Grichuk</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-18T00:40:00Z</t>
+          <t>2026-08-18T00:05:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Tomoyuki Sugano</t>
+          <t>Shota Imanaga</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>608372</t>
+          <t>684007</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>58.5</v>
+        <v>58.3</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -14004,26 +14004,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable, Good Environment, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>33.5</v>
+        <v>51.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>73.3</v>
+        <v>53</v>
       </c>
       <c r="R12" t="n">
-        <v>79.7</v>
+        <v>40.3</v>
       </c>
       <c r="S12" t="n">
-        <v>76.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>43.8</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -14075,12 +14075,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -14090,12 +14090,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/23, 0 HR</t>
+          <t>Contact streak: 7/17 over last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 13.1% barrel, 26.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 28.9 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -14105,112 +14105,112 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>38.58</t>
+          <t>48.59</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.12</t>
+          <t>91.56</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>98.8499</t>
+          <t>103.0646</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4165</t>
+          <t>0.4724</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1549</t>
+          <t>0.197</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.3344</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>71.51</t>
+          <t>74.18</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>43.17</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>43.66</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>27.52</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>0.2332</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>10.27</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>90.49</t>
+          <t>89.02</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>0.4298</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>0.1933</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>34.39</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -14270,7 +14270,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>56.9</v>
+        <v>56</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
         <v>53.1</v>
       </c>
       <c r="R13" t="n">
-        <v>46.3</v>
+        <v>40.3</v>
       </c>
       <c r="S13" t="n">
         <v>100</v>
@@ -14480,12 +14480,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -14501,47 +14501,47 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>683737</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Michael Busch</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-18T00:05:00Z</t>
+          <t>2026-08-18T00:40:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Luis Castillo</t>
+          <t>Tomoyuki Sugano</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>622491</t>
+          <t>608372</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -14564,26 +14564,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Pitcher Vulnerable, Good Environment</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>43.5</v>
+        <v>41</v>
       </c>
       <c r="Q14" t="n">
-        <v>53.1</v>
+        <v>73.3</v>
       </c>
       <c r="R14" t="n">
-        <v>46.3</v>
+        <v>79.7</v>
       </c>
       <c r="S14" t="n">
-        <v>96.59999999999999</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>23.4</v>
+        <v>21.5</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -14597,7 +14597,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -14635,12 +14635,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -14650,127 +14650,127 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 5/19, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.8% barrel, 18.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 13.1% barrel, 26.7 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>11.36</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>44.07</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>89.26</t>
+          <t>89.85</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>99.5152</t>
+          <t>101.0244</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.2013</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3444</t>
+          <t>0.316</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>24.99</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1773</t>
+          <t>0.165</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>42.32</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>90.16</t>
+          <t>90.49</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.4334</t>
+          <t>0.552</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.249</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -14781,12 +14781,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>676439</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Teoscar Hernández</t>
+          <t>Hunter Feduccia</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -14811,7 +14811,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -14830,7 +14830,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>56</v>
+        <v>55.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -14844,11 +14844,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable, Good Environment</t>
+          <t>Pitcher Vulnerable, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="Q15" t="n">
         <v>73.3</v>
@@ -14857,13 +14857,13 @@
         <v>79.7</v>
       </c>
       <c r="S15" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>21.5</v>
+        <v>43.2</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -14915,27 +14915,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 0 HR</t>
+          <t>Last 7 games: 4/14, 1 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 13.1% barrel, 26.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 13.1% barrel, 26.7 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -14945,67 +14945,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>44.07</t>
+          <t>37.84</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>89.85</t>
+          <t>89.56</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>101.0244</t>
+          <t>99.1664</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.3664</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.1325</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>0.3065</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>70.78</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>13.05</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>32.38</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>27.38</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>0.099</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -15061,47 +15061,47 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>676439</t>
+          <t>683737</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hunter Feduccia</t>
+          <t>Michael Busch</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-18T00:40:00Z</t>
+          <t>2026-08-18T00:05:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Tomoyuki Sugano</t>
+          <t>Luis Castillo</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>608372</t>
+          <t>622491</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -15110,7 +15110,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>55.4</v>
+        <v>55.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -15124,26 +15124,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable, Good Environment, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>31</v>
+        <v>43.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>73.3</v>
+        <v>53.1</v>
       </c>
       <c r="R16" t="n">
-        <v>79.7</v>
+        <v>40.3</v>
       </c>
       <c r="S16" t="n">
-        <v>44.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>43.2</v>
+        <v>23.4</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -15195,142 +15195,142 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/14, 1 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 13.1% barrel, 26.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.8% barrel, 18.8 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>11.36</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>37.84</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>89.56</t>
+          <t>89.26</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.1664</t>
+          <t>99.5152</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3664</t>
+          <t>0.443</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1325</t>
+          <t>0.2013</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3065</t>
+          <t>0.3444</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>70.78</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>0.1773</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>90.49</t>
+          <t>90.16</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>0.4334</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr"/>
@@ -15341,47 +15341,47 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>664023</t>
+          <t>669242</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ian Happ</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-18T00:05:00Z</t>
+          <t>2026-08-18T00:40:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Luis Castillo</t>
+          <t>Tomoyuki Sugano</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>622491</t>
+          <t>608372</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -15390,7 +15390,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>54.3</v>
+        <v>54.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -15404,26 +15404,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Pitcher Vulnerable, Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>43.1</v>
+        <v>23.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>51.1</v>
+        <v>72.2</v>
       </c>
       <c r="R17" t="n">
-        <v>46.3</v>
+        <v>79.7</v>
       </c>
       <c r="S17" t="n">
-        <v>86.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
         <v>75</v>
       </c>
       <c r="U17" t="n">
-        <v>39.5</v>
+        <v>27.6</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -15475,12 +15475,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -15490,127 +15490,127 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 1 HR</t>
+          <t>Last 7 games: 4/22, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.8% barrel, 18.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 13.1% barrel, 26.7 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>10.82</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>42.72</t>
+          <t>36.75</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>89.44</t>
+          <t>88.23</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>100.83</t>
+          <t>99.3821</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>0.3844</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1916</t>
+          <t>0.1202</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3225</t>
+          <t>0.3161</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>71.88</t>
+          <t>70.52</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>12.32</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>41.97</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>26.08</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1903</t>
+          <t>0.1423</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>9.84</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>42.32</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>90.16</t>
+          <t>90.49</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.4334</t>
+          <t>0.552</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.249</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>28.28</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>88</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr"/>
@@ -15621,47 +15621,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>664023</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Ian Happ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-18T00:40:00Z</t>
+          <t>2026-08-18T00:05:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Tomoyuki Sugano</t>
+          <t>Luis Castillo</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>608372</t>
+          <t>622491</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -15670,7 +15670,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>54.2</v>
+        <v>53.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -15684,26 +15684,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Pitcher Vulnerable, Good Environment, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>23.6</v>
+        <v>43.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>72.2</v>
+        <v>51.1</v>
       </c>
       <c r="R18" t="n">
-        <v>79.7</v>
+        <v>40.3</v>
       </c>
       <c r="S18" t="n">
-        <v>64.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T18" t="n">
         <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>27.6</v>
+        <v>39.5</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -15755,12 +15755,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -15770,127 +15770,127 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 1 HR</t>
+          <t>Last 7 games: 6/23, 1 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 13.1% barrel, 26.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.8% barrel, 18.8 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>10.82</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>36.75</t>
+          <t>42.72</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>89.44</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>99.3821</t>
+          <t>100.83</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3844</t>
+          <t>0.408</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1202</t>
+          <t>0.1916</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3161</t>
+          <t>0.3225</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>70.52</t>
+          <t>71.88</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>41.97</t>
+          <t>43.77</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>26.08</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1423</t>
+          <t>0.1903</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>9.84</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>90.49</t>
+          <t>90.16</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>0.4334</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>28.28</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr"/>
@@ -15950,7 +15950,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>51.5</v>
+        <v>50.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>53.1</v>
       </c>
       <c r="R19" t="n">
-        <v>46.3</v>
+        <v>40.3</v>
       </c>
       <c r="S19" t="n">
         <v>52.4</v>
@@ -16160,12 +16160,12 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -16230,7 +16230,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>50.5</v>
+        <v>49.6</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>53.1</v>
       </c>
       <c r="R20" t="n">
-        <v>46.3</v>
+        <v>40.3</v>
       </c>
       <c r="S20" t="n">
         <v>94.90000000000001</v>
@@ -16440,12 +16440,12 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -16510,7 +16510,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>47</v>
+        <v>46.1</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>53</v>
       </c>
       <c r="R21" t="n">
-        <v>46.3</v>
+        <v>40.3</v>
       </c>
       <c r="S21" t="n">
         <v>76.2</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
